--- a/source/LTU/GF_LTU.xlsx
+++ b/source/LTU/GF_LTU.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a1234414/Desktop/TEAMS/GF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385523FE-ACC5-AA48-B58D-16DF4A9516F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32C2BD49-BEF2-4895-9163-F618CCEA0BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30480" yWindow="3080" windowWidth="26840" windowHeight="15760" firstSheet="1" activeTab="1" xr2:uid="{AC72BA3D-1AAC-7842-9A39-CB31A98D4FB1}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="2" r:id="rId1"/>
-    <sheet name="growth facility list" sheetId="1" r:id="rId2"/>
+    <sheet name="growth facility" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="43">
   <si>
     <t>Template to record Growth facilities information</t>
   </si>
@@ -72,16 +72,52 @@
     <t>For any questions, please contact Liliana Andres at liliana.andreshernandez@adelaide.edu.au.</t>
   </si>
   <si>
+    <t>organisation</t>
+  </si>
+  <si>
+    <t>growth facility name *</t>
+  </si>
+  <si>
+    <t>growth facility description *</t>
+  </si>
+  <si>
+    <t>growth facility type *</t>
+  </si>
+  <si>
+    <t>growth facility type brand *</t>
+  </si>
+  <si>
+    <t>growth facility model *</t>
+  </si>
+  <si>
+    <t>growth facility serial number *</t>
+  </si>
+  <si>
+    <t>containment level *</t>
+  </si>
+  <si>
+    <t>quarantine details *</t>
+  </si>
+  <si>
+    <t>growth facility ontology label</t>
+  </si>
+  <si>
+    <t>growth facility ontology ID</t>
+  </si>
+  <si>
+    <t>growth facility ontology IRI</t>
+  </si>
+  <si>
     <t>LTU</t>
   </si>
   <si>
-    <t>RD4A Compartment 101</t>
+    <t>RD4A compartment 101</t>
   </si>
   <si>
     <t>100sqm Glasshouse with fertigation, temp, humidity and supplemental LED lighting (Cool-White,Blue, Red, Far-Red) control, includes black out curtains to control photoperiod</t>
   </si>
   <si>
-    <t>Controlled environment glasshouse</t>
+    <t>controlled environment glasshouse</t>
   </si>
   <si>
     <t>Fertigation, Temp, Humidity: PRIVA, LEDs: PSI</t>
@@ -96,37 +132,46 @@
     <t>No</t>
   </si>
   <si>
-    <t>RD4A Compartment 102</t>
+    <t>greenhouse</t>
+  </si>
+  <si>
+    <t>ENVO:03600087</t>
+  </si>
+  <si>
+    <t>http://purl.obolibrary.org/obo/ENVO_03600087</t>
+  </si>
+  <si>
+    <t>RD4A compartment 102</t>
   </si>
   <si>
     <t>100sqm Closed environment phenotyping room with fertigation, temp, humidity and LED lighting (Cool-White,Red, Far-Red)</t>
   </si>
   <si>
-    <t>Controlled environment room</t>
-  </si>
-  <si>
-    <t>RD4A Compartment 103</t>
+    <t>controlled environment room</t>
+  </si>
+  <si>
+    <t>RD4A compartment 103</t>
   </si>
   <si>
     <t>100sqm Glasshouse with fertigation, temp, humidity and LED supplemental lighting (Cool-White,Blue, Red, Far-Red) control, includes black out curtains to control photoperiod</t>
   </si>
   <si>
-    <t>RD4A Compartment 104</t>
+    <t>RD4A compartment 104</t>
   </si>
   <si>
     <t>100sqm Glasshouse with fertigation, temp, humidity and supplemental LED lighting (Cool-White,Blue, Red, Far-Red) control</t>
   </si>
   <si>
-    <t>RD4A Compartment 105</t>
+    <t>RD4A compartment 105</t>
   </si>
   <si>
     <t>100sqm Closed environment phenotyping room with fertigation, temp, humidity and LED lighting (Cool-White,Blue, Red, Far-Red)</t>
   </si>
   <si>
-    <t>RD4A Compartment 106</t>
-  </si>
-  <si>
-    <t>RD4A Compartment 107</t>
+    <t>RD4A compartment 106</t>
+  </si>
+  <si>
+    <t>RD4A compartment 107</t>
   </si>
   <si>
     <t>30sqm Glasshouse with fertigation, temp, humidity and supplemental LED lighting (Cool-White,Blue, Red, Far-Red) control</t>
@@ -139,62 +184,19 @@
   </si>
   <si>
     <t>Temp, Humidity: AgriBio, LEDs: PSI</t>
-  </si>
-  <si>
-    <t>organization</t>
-  </si>
-  <si>
-    <t>growth facility name *</t>
-  </si>
-  <si>
-    <t>growth facility description *</t>
-  </si>
-  <si>
-    <t>growth facility type *</t>
-  </si>
-  <si>
-    <t>growth facility type brand *</t>
-  </si>
-  <si>
-    <t>growth facility model *</t>
-  </si>
-  <si>
-    <t>growth facility serial number *</t>
-  </si>
-  <si>
-    <t>containment level *</t>
-  </si>
-  <si>
-    <t>quarantine *</t>
-  </si>
-  <si>
-    <t>growth facility ontology label</t>
-  </si>
-  <si>
-    <t>growth facility ontology ID</t>
-  </si>
-  <si>
-    <t>growth facility ontology IRI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
@@ -228,31 +230,25 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -323,47 +319,46 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -711,45 +706,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7D041E5-B153-46FE-B195-25B032F510B5}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="185.1640625" style="5" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="185.125" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:1" ht="26.1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="22" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:1" ht="21.95">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-    </row>
-    <row r="4" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-    </row>
-    <row r="5" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="3" spans="1:1" ht="21">
+      <c r="A3" s="6"/>
+    </row>
+    <row r="4" spans="1:1" ht="21">
+      <c r="A4" s="6"/>
+    </row>
+    <row r="5" spans="1:1" ht="21">
+      <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="44" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:1" ht="44.1">
+      <c r="A6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:1" ht="21">
+      <c r="A7" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+    <row r="8" spans="1:1" ht="21">
+      <c r="A8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -758,323 +753,347 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F732A2EF-4BDF-CC42-987B-080B1E91E6E2}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="35.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="35.625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="23.83203125" customWidth="1"/>
+    <col min="1" max="1" width="23.875" customWidth="1"/>
     <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="110.5" customWidth="1"/>
-    <col min="7" max="7" width="41.5" customWidth="1"/>
+    <col min="5" max="5" width="56.75" customWidth="1"/>
+    <col min="7" max="7" width="33.75" customWidth="1"/>
+    <col min="8" max="8" width="20.875" customWidth="1"/>
+    <col min="9" max="9" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="18.75">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="2" customFormat="1">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" s="2" customFormat="1" ht="15.95">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="C4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="C5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="I9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>12</v>
-      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L2" r:id="rId1" xr:uid="{6714F7B0-CA06-45B7-A72D-73A05BE0816D}"/>
+    <hyperlink ref="L4" r:id="rId2" xr:uid="{CBD0A0C3-743C-4DE4-BF35-53AB8DF4CCD9}"/>
+    <hyperlink ref="L5" r:id="rId3" xr:uid="{A20CD933-5499-4CC7-AA12-848A9EDA7E5C}"/>
+    <hyperlink ref="L7" r:id="rId4" xr:uid="{52AFB6DC-C5AD-49B0-B1DD-796089A0C1E9}"/>
+    <hyperlink ref="L8" r:id="rId5" xr:uid="{92D32B98-C65D-4270-BA83-82145B5FA7D9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Image xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949" xsi:nil="true"/>
-    <TaxCatchAll xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23" xsi:nil="true"/>
-    <l544f18d430f4c0886024d9e622455c4 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </l544f18d430f4c0886024d9e622455c4>
-    <jbe33349d2e04ad58f3e9557e0157918 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </jbe33349d2e04ad58f3e9557e0157918>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <f876555452e44e5798dee990952b63ae xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </f876555452e44e5798dee990952b63ae>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007EE926928A949E41B5C68441ED11B2EA" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="52be21af1a8349f18767d387bddd8232">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b2ccdccd-44c9-4047-9c28-347bfbb7eb23" xmlns:ns3="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="10d9f1abffa380d50643d816c40c845c" ns2:_="" ns3:_="">
     <xsd:import namespace="b2ccdccd-44c9-4047-9c28-347bfbb7eb23"/>
@@ -1329,30 +1348,51 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Image xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949" xsi:nil="true"/>
+    <TaxCatchAll xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23" xsi:nil="true"/>
+    <l544f18d430f4c0886024d9e622455c4 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </l544f18d430f4c0886024d9e622455c4>
+    <jbe33349d2e04ad58f3e9557e0157918 xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </jbe33349d2e04ad58f3e9557e0157918>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c57c0e25-d6d6-4f5b-b0b2-7d758d7a4949">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <f876555452e44e5798dee990952b63ae xmlns="b2ccdccd-44c9-4047-9c28-347bfbb7eb23">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f876555452e44e5798dee990952b63ae>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="d560fd02-aa12-447b-bf2e-34c9e57d035a" ContentTypeId="0x0101" PreviousValue="false"/>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8259D85E-FD19-4986-AAF0-D60D4C88F96A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DA5440D-BB52-4233-8043-2E488FDC4471}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAAEE57-DF72-459C-9353-2868B0846A53}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AAAEE57-DF72-459C-9353-2868B0846A53}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DA5440D-BB52-4233-8043-2E488FDC4471}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8259D85E-FD19-4986-AAF0-D60D4C88F96A}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
